--- a/menu.xlsx
+++ b/menu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>1단계_ID</t>
   </si>
@@ -73,7 +73,7 @@
     <t>A2a</t>
   </si>
   <si>
-    <t>📊 미정산 내역</t>
+    <t>미정산 내역</t>
   </si>
   <si>
     <t>unsettled_details</t>
@@ -85,7 +85,7 @@
     <t>A2b</t>
   </si>
   <si>
-    <t>💰 실행예산잔액</t>
+    <t>실행예산잔액</t>
   </si>
   <si>
     <t>budget_balance</t>
@@ -97,7 +97,7 @@
     <t>A2c</t>
   </si>
   <si>
-    <t>📋 연구활동비 상세</t>
+    <t>연구활동비 상세</t>
   </si>
   <si>
     <t>research_details</t>
@@ -115,58 +115,85 @@
     <t>B1</t>
   </si>
   <si>
-    <t>연구비 규정</t>
+    <t>과제번호·기타</t>
   </si>
   <si>
     <t>TEXT</t>
   </si>
   <si>
-    <t>budget_rule</t>
-  </si>
-  <si>
-    <t>연구비 사용 한도·집행 규정 안내</t>
+    <t>budget_rule1</t>
+  </si>
+  <si>
+    <t>과제 번호 및 기타 안내</t>
   </si>
   <si>
     <t>B2</t>
   </si>
   <si>
-    <t>출장 규정</t>
-  </si>
-  <si>
-    <t>B2a</t>
-  </si>
-  <si>
-    <t>🇰🇷 국내 출장</t>
-  </si>
-  <si>
-    <t>travel_domestic</t>
-  </si>
-  <si>
-    <t>국내 출장 일비·숙박비 규정</t>
-  </si>
-  <si>
-    <t>B2b</t>
-  </si>
-  <si>
-    <t>✈️ 해외 출장</t>
-  </si>
-  <si>
-    <t>travel_overseas</t>
-  </si>
-  <si>
-    <t>해외 출장 규정</t>
+    <t>카드 재사용·재발급</t>
+  </si>
+  <si>
+    <t>budget_rule2</t>
+  </si>
+  <si>
+    <t>연구비 카드 재사용/재발급 신청</t>
   </si>
   <si>
     <t>B3</t>
   </si>
   <si>
-    <t>장비 예약</t>
-  </si>
-  <si>
-    <t>equipment_rule</t>
-  </si>
-  <si>
-    <t>공용 장비 예약 절차 안내</t>
+    <t>물품·재료</t>
+  </si>
+  <si>
+    <t>budget_rule3</t>
+  </si>
+  <si>
+    <t>물품·재료 구입 증빙서류</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>도서·SW·논문</t>
+  </si>
+  <si>
+    <t>budget_rule4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>회의·세미나</t>
+  </si>
+  <si>
+    <t>budget_rule5</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>출장비</t>
+  </si>
+  <si>
+    <t>budget_rule6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>교육·훈련·학회</t>
+  </si>
+  <si>
+    <t>budget_rule7</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>전문가·일용직</t>
+  </si>
+  <si>
+    <t>budget_rule8</t>
   </si>
   <si>
     <t>C</t>
@@ -178,13 +205,25 @@
     <t>C1</t>
   </si>
   <si>
-    <t>🔗 링크</t>
+    <t>링크</t>
   </si>
   <si>
     <t>work_link</t>
   </si>
   <si>
     <t>행정 업무 링크</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>인수인계</t>
+  </si>
+  <si>
+    <t>work_handover</t>
+  </si>
+  <si>
+    <t>행정실무사 인수인계</t>
   </si>
   <si>
     <t>D</t>
@@ -304,8 +343,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
@@ -315,7 +353,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="1"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -390,10 +428,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="&amp;amp;amp;#xFF2D;&amp;amp;amp;#xFF33; &amp;amp;amp;#xFF30;&amp;amp;amp;#x30B4;&amp;amp;amp;#x30B7;&amp;amp;amp;#x30C3;&amp;amp;amp;#x30AF;"/>
-        <a:font script="Hang" typeface="&amp;amp;amp;#xB9D1;&amp;amp;amp;#xC740; &amp;amp;amp;#xACE0;&amp;amp;amp;#xB515;"/>
-        <a:font script="Hans" typeface="&amp;amp;amp;#x5B8B;&amp;amp;amp;#x4F53;"/>
-        <a:font script="Hant" typeface="&amp;amp;amp;#x65B0;&amp;amp;amp;#x7D30;&amp;amp;amp;#x660E;&amp;amp;amp;#x9AD4;"/>
+        <a:font script="Jpan" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xFF2D;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xFF33; &amp;amp;amp;amp;amp;amp;amp;amp;amp;#xFF30;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30B4;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30B7;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30C3;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xB9D1;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xC740; &amp;amp;amp;amp;amp;amp;amp;amp;amp;#xACE0;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x5B8B;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x65B0;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x7D30;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x660E;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -424,10 +462,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="&amp;amp;amp;#xFF2D;&amp;amp;amp;#xFF33; &amp;amp;amp;#xFF30;&amp;amp;amp;#x30B4;&amp;amp;amp;#x30B7;&amp;amp;amp;#x30C3;&amp;amp;amp;#x30AF;"/>
-        <a:font script="Hang" typeface="&amp;amp;amp;#xB9D1;&amp;amp;amp;#xC740; &amp;amp;amp;#xACE0;&amp;amp;amp;#xB515;"/>
-        <a:font script="Hans" typeface="&amp;amp;amp;#x5B8B;&amp;amp;amp;#x4F53;"/>
-        <a:font script="Hant" typeface="&amp;amp;amp;#x65B0;&amp;amp;amp;#x7D30;&amp;amp;amp;#x660E;&amp;amp;amp;#x9AD4;"/>
+        <a:font script="Jpan" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xFF2D;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xFF33; &amp;amp;amp;amp;amp;amp;amp;amp;amp;#xFF30;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30B4;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30B7;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30C3;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xB9D1;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xC740; &amp;amp;amp;amp;amp;amp;amp;amp;amp;#xACE0;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x5B8B;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x65B0;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x7D30;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x660E;&amp;amp;amp;amp;amp;amp;amp;amp;amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -628,8 +666,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F5AC8E87-11F8-4753-A561-C5A73CBCFBA2}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:I12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0B4CE007-D027-4CD8-A01C-244748F65EAB}" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
     <col min="1" max="1" style="1" width="12.00390625" customWidth="1"/>
@@ -822,20 +860,16 @@
       <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="1" customFormat="1">
@@ -846,25 +880,21 @@
         <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="1" customFormat="1">
@@ -875,10 +905,10 @@
         <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -886,24 +916,24 @@
         <v>34</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="1" customFormat="1">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -911,49 +941,49 @@
         <v>34</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="1" customFormat="1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="1" customFormat="1">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -961,12 +991,139 @@
         <v>34</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1" customFormat="1">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="1" customFormat="1">
+      <c r="A14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="1" customFormat="1">
+      <c r="A15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="1" customFormat="1">
+      <c r="A16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="1" customFormat="1">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="1" customFormat="1"/>
+    <row r="19" ht="15" customHeight="1" s="1" customFormat="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -980,7 +1137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{41DDDEFB-24D5-42C3-BC7E-24625412E72F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B801AEBC-04C9-46D8-86BB-A857B344A454}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -990,7 +1147,7 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -1001,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="1" customFormat="1">
@@ -1009,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="1" customFormat="1">
@@ -1017,7 +1174,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="1" customFormat="1">
@@ -1025,7 +1182,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="1" customFormat="1">
@@ -1033,7 +1190,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="1" customFormat="1">
@@ -1042,34 +1199,34 @@
     </row>
     <row r="8" ht="15" customHeight="1" s="1" customFormat="1">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="1" customFormat="1">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="1" customFormat="1">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="1" customFormat="1">
       <c r="A11" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
